--- a/cv/cv.xlsx
+++ b/cv/cv.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\ubuntu\mnt\tsys\repos\CV-Awesome\cv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5E3D8C9-6FD0-4190-AD79-9C5AC5A828C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B6D92CA-7F81-472D-8A7A-B3D009CB7F45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="2688" windowWidth="23040" windowHeight="9540" tabRatio="500" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="education" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="109">
   <si>
     <t>degree</t>
   </si>
@@ -337,6 +337,27 @@
   </si>
   <si>
     <t>AWK</t>
+  </si>
+  <si>
+    <t>Jul 2023</t>
+  </si>
+  <si>
+    <t>May 2026</t>
+  </si>
+  <si>
+    <t>Jul 2023--May 2026</t>
+  </si>
+  <si>
+    <t>Deputy Head of Department (in charge) of Financial Investment</t>
+  </si>
+  <si>
+    <t>Jun 2026</t>
+  </si>
+  <si>
+    <t>Director of Insurance Program</t>
+  </si>
+  <si>
+    <t>Jun 2026--Present</t>
   </si>
 </sst>
 </file>
@@ -952,14 +973,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultColWidth="10.5" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.296875" customWidth="1"/>
-    <col min="2" max="2" width="20.296875" customWidth="1"/>
+    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="54.8984375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.59765625" customWidth="1"/>
     <col min="4" max="4" width="10.19921875" customWidth="1"/>
-    <col min="6" max="6" width="12.796875" customWidth="1"/>
+    <col min="6" max="6" width="17.09765625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -1145,6 +1167,11 @@
       <c r="G8" t="s">
         <v>49</v>
       </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
@@ -1793,8 +1820,14 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="55.69921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.09765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.09765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.09765625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -1817,6 +1850,46 @@
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/cv/cv.xlsx
+++ b/cv/cv.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\ubuntu\mnt\tsys\repos\CV-Awesome\cv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B6D92CA-7F81-472D-8A7A-B3D009CB7F45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CDB68DD-9D7B-45E0-BE34-D9564466B87A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2688" windowWidth="23040" windowHeight="9540" tabRatio="500" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="education" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="leadership" sheetId="6" r:id="rId6"/>
     <sheet name="skills" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="120">
   <si>
     <t>degree</t>
   </si>
@@ -358,6 +358,39 @@
   </si>
   <si>
     <t>Jun 2026--Present</t>
+  </si>
+  <si>
+    <t>Visiting Lecturer</t>
+  </si>
+  <si>
+    <t>University of Economics HCMC (UEH)</t>
+  </si>
+  <si>
+    <t>HCMC Open University (OU)</t>
+  </si>
+  <si>
+    <t>Jan 2026</t>
+  </si>
+  <si>
+    <t>Jan 2026--Present</t>
+  </si>
+  <si>
+    <t>FPT School of Business &amp; Technology (FSB)</t>
+  </si>
+  <si>
+    <t>Sep 2024</t>
+  </si>
+  <si>
+    <t>Sep 2024--Present</t>
+  </si>
+  <si>
+    <t>Financial Analysis (LBU)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Investment Analysis and Management </t>
+  </si>
+  <si>
+    <t>Advanced Investment Analysis and Management</t>
   </si>
 </sst>
 </file>
@@ -973,10 +1006,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultColWidth="10.5" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.3984375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="54.8984375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.59765625" customWidth="1"/>
     <col min="4" max="4" width="10.19921875" customWidth="1"/>
@@ -1012,7 +1045,7 @@
         <v>39</v>
       </c>
       <c r="B2" t="s">
-        <v>40</v>
+        <v>111</v>
       </c>
       <c r="C2" t="s">
         <v>16</v>
@@ -1035,7 +1068,7 @@
         <v>39</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>111</v>
       </c>
       <c r="C3" t="s">
         <v>16</v>
@@ -1058,7 +1091,7 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>40</v>
+        <v>111</v>
       </c>
       <c r="C4" t="s">
         <v>16</v>
@@ -1081,7 +1114,7 @@
         <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>40</v>
+        <v>111</v>
       </c>
       <c r="C5" t="s">
         <v>16</v>
@@ -1104,7 +1137,7 @@
         <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>40</v>
+        <v>111</v>
       </c>
       <c r="C6" t="s">
         <v>16</v>
@@ -1127,7 +1160,7 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>40</v>
+        <v>111</v>
       </c>
       <c r="C7" t="s">
         <v>16</v>
@@ -1150,7 +1183,7 @@
         <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>40</v>
+        <v>111</v>
       </c>
       <c r="C8" t="s">
         <v>16</v>
@@ -1169,9 +1202,73 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
+      <c r="A9" t="s">
+        <v>109</v>
+      </c>
+      <c r="B9" t="s">
+        <v>114</v>
+      </c>
+      <c r="C9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="E9" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" t="s">
+        <v>116</v>
+      </c>
+      <c r="G9" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>109</v>
+      </c>
+      <c r="B10" t="s">
+        <v>110</v>
+      </c>
+      <c r="C10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="G10" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>109</v>
+      </c>
+      <c r="B11" t="s">
+        <v>110</v>
+      </c>
+      <c r="C11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>119</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
